--- a/artfynd/A 25435-2023 artfynd.xlsx
+++ b/artfynd/A 25435-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25435-2023 artfynd.xlsx
+++ b/artfynd/A 25435-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110970739</v>
+        <v>110954667</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571982.3457646836</v>
+        <v>572038</v>
       </c>
       <c r="R2" t="n">
-        <v>6409261.589547437</v>
+        <v>6409296</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,24 +755,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 knopp</t>
+          <t>Flög upp från branten ovh upp mot berget</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -812,12 +792,7 @@
         <v>110970677</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,6 +906,135 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>110970739</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 25435, Skälhem, Hallingeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571982</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6409262</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 knopp</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
